--- a/artfynd/A 10780-2021 artfynd.xlsx
+++ b/artfynd/A 10780-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121586352</v>
+        <v>121586305</v>
       </c>
       <c r="B2" t="n">
-        <v>57297</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102622</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -720,17 +720,21 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skogen, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389171</v>
+        <v>389169</v>
       </c>
       <c r="R2" t="n">
-        <v>6265614</v>
+        <v>6265654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121585969</v>
+        <v>121585981</v>
       </c>
       <c r="B3" t="n">
-        <v>57314</v>
+        <v>57318</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +805,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102975</v>
+        <v>100020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Berguv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Bubo bubo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -871,12 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121586305</v>
+        <v>121585969</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>57314</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,16 +923,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102975</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -938,16 +942,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -955,14 +955,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogen, Hl</t>
+          <t>Södra Kattarp, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389169</v>
+        <v>389124</v>
       </c>
       <c r="R4" t="n">
-        <v>6265654</v>
+        <v>6265686</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,12 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585981</v>
+        <v>121586352</v>
       </c>
       <c r="B5" t="n">
-        <v>57318</v>
+        <v>57297</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,20 +1033,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100020</v>
+        <v>102622</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Berguv</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bubo bubo</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Kattarp, Hl</t>
+          <t>Skogen, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>389124</v>
+        <v>389171</v>
       </c>
       <c r="R5" t="n">
-        <v>6265686</v>
+        <v>6265614</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 10780-2021 artfynd.xlsx
+++ b/artfynd/A 10780-2021 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121585969</v>
+        <v>121586352</v>
       </c>
       <c r="B4" t="n">
-        <v>57314</v>
+        <v>57297</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,20 +919,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102975</v>
+        <v>102622</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,22 +947,22 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Kattarp, Hl</t>
+          <t>Skogen, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389124</v>
+        <v>389171</v>
       </c>
       <c r="R4" t="n">
-        <v>6265686</v>
+        <v>6265614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,12 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121586352</v>
+        <v>121585969</v>
       </c>
       <c r="B5" t="n">
-        <v>57297</v>
+        <v>57314</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,20 +1033,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102622</v>
+        <v>102975</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogen, Hl</t>
+          <t>Södra Kattarp, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>389171</v>
+        <v>389124</v>
       </c>
       <c r="R5" t="n">
-        <v>6265614</v>
+        <v>6265686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 10780-2021 artfynd.xlsx
+++ b/artfynd/A 10780-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121586305</v>
+        <v>121585981</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Berguv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bubo bubo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,16 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -727,14 +723,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogen, Hl</t>
+          <t>Södra Kattarp, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389169</v>
+        <v>389124</v>
       </c>
       <c r="R2" t="n">
-        <v>6265654</v>
+        <v>6265686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,12 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121585981</v>
+        <v>121586352</v>
       </c>
       <c r="B3" t="n">
-        <v>57318</v>
+        <v>57298</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100020</v>
+        <v>102622</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Berguv</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bubo bubo</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,22 +829,22 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södra Kattarp, Hl</t>
+          <t>Skogen, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389124</v>
+        <v>389171</v>
       </c>
       <c r="R3" t="n">
-        <v>6265686</v>
+        <v>6265614</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,12 +871,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121586352</v>
+        <v>121586305</v>
       </c>
       <c r="B4" t="n">
-        <v>57297</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,20 +915,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102622</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -942,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -952,17 +948,21 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogen, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389171</v>
+        <v>389169</v>
       </c>
       <c r="R4" t="n">
-        <v>6265614</v>
+        <v>6265654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,12 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
         <v>121585969</v>
       </c>
       <c r="B5" t="n">
-        <v>57314</v>
+        <v>57315</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2021 artfynd.xlsx
+++ b/artfynd/A 10780-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121585981</v>
+        <v>121586305</v>
       </c>
       <c r="B2" t="n">
-        <v>57319</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100020</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Berguv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bubo bubo</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,12 +710,16 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -723,14 +727,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra Kattarp, Hl</t>
+          <t>Skogen, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389124</v>
+        <v>389169</v>
       </c>
       <c r="R2" t="n">
-        <v>6265686</v>
+        <v>6265654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,12 +761,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121585969</v>
+        <v>121586352</v>
       </c>
       <c r="B3" t="n">
-        <v>57315</v>
+        <v>57298</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +805,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102975</v>
+        <v>102622</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -829,22 +833,22 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södra Kattarp, Hl</t>
+          <t>Skogen, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389124</v>
+        <v>389171</v>
       </c>
       <c r="R3" t="n">
-        <v>6265686</v>
+        <v>6265614</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,12 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121586305</v>
+        <v>121585981</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>57319</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,20 +919,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Berguv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bubo bubo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -938,16 +942,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -955,14 +955,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogen, Hl</t>
+          <t>Södra Kattarp, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389169</v>
+        <v>389124</v>
       </c>
       <c r="R4" t="n">
-        <v>6265654</v>
+        <v>6265686</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,12 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121586352</v>
+        <v>121585969</v>
       </c>
       <c r="B5" t="n">
-        <v>57298</v>
+        <v>57315</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,20 +1033,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102622</v>
+        <v>102975</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogen, Hl</t>
+          <t>Södra Kattarp, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>389171</v>
+        <v>389124</v>
       </c>
       <c r="R5" t="n">
-        <v>6265614</v>
+        <v>6265686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 10780-2021 artfynd.xlsx
+++ b/artfynd/A 10780-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121586305</v>
+        <v>121585969</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>57315</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102975</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,16 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -727,14 +723,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogen, Hl</t>
+          <t>Södra Kattarp, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389169</v>
+        <v>389124</v>
       </c>
       <c r="R2" t="n">
-        <v>6265654</v>
+        <v>6265686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,12 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121586352</v>
+        <v>121586305</v>
       </c>
       <c r="B3" t="n">
-        <v>57298</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102622</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -838,17 +834,21 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogen, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389171</v>
+        <v>389169</v>
       </c>
       <c r="R3" t="n">
-        <v>6265614</v>
+        <v>6265654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,12 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121585981</v>
+        <v>121586352</v>
       </c>
       <c r="B4" t="n">
-        <v>57319</v>
+        <v>57298</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,20 +919,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100020</v>
+        <v>102622</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Berguv</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bubo bubo</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,22 +947,22 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Kattarp, Hl</t>
+          <t>Skogen, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389124</v>
+        <v>389171</v>
       </c>
       <c r="R4" t="n">
-        <v>6265686</v>
+        <v>6265614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,12 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585969</v>
+        <v>121585981</v>
       </c>
       <c r="B5" t="n">
-        <v>57315</v>
+        <v>57319</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,20 +1033,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102975</v>
+        <v>100020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Berguv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Bubo bubo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 10780-2021 artfynd.xlsx
+++ b/artfynd/A 10780-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121585969</v>
       </c>
       <c r="B2" t="n">
-        <v>57501</v>
+        <v>57502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2021 artfynd.xlsx
+++ b/artfynd/A 10780-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121585969</v>
       </c>
       <c r="B2" t="n">
-        <v>57502</v>
+        <v>57506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 10780-2021 artfynd.xlsx
+++ b/artfynd/A 10780-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121585969</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
